--- a/appraiser_forms/032_rarity_assessment_form--appraiser_forms.xlsx
+++ b/appraiser_forms/032_rarity_assessment_form--appraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'us',_'value':_'us'}</t>
+          <t>us</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'US', 'value': 'US'}</t>
+          <t>US</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'canada',_'value':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Canada', 'value': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'uk',_'value':_'uk'}</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'UK', 'value': 'UK'}</t>
+          <t>UK</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_common',_'value':_1}</t>
+          <t>1_-_common</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '1 - Common', 'value': 1}</t>
+          <t>1 - Common</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_uncommon',_'value':_2}</t>
+          <t>2_-_uncommon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '2 - Uncommon', 'value': 2}</t>
+          <t>2 - Uncommon</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_rare',_'value':_3}</t>
+          <t>3_-_rare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '3 - Rare', 'value': 3}</t>
+          <t>3 - Rare</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_very_rare',_'value':_4}</t>
+          <t>4_-_very_rare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '4 - Very Rare', 'value': 4}</t>
+          <t>4 - Very Rare</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_extremely_rare',_'value':_5}</t>
+          <t>5_-_extremely_rare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '5 - Extremely Rare', 'value': 5}</t>
+          <t>5 - Extremely Rare</t>
         </is>
       </c>
     </row>
